--- a/data/01_QC/sequencing statistics.xlsx
+++ b/data/01_QC/sequencing statistics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BoxDrive\Box\Science\Fisheries\Projects\Epigenetic Aging\github\Epigenetic_aging_haddock\data\01_QC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E2192D-ED99-4B58-9BD6-ED4400BB8860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3D2F1A-8358-4686-9000-E5DCBD06C958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="296">
   <si>
     <t>Sample Name</t>
   </si>
@@ -894,6 +894,36 @@
   </si>
   <si>
     <t>Mean % Dups</t>
+  </si>
+  <si>
+    <t>Coverage</t>
+  </si>
+  <si>
+    <t>Genome size</t>
+  </si>
+  <si>
+    <t>Mb</t>
+  </si>
+  <si>
+    <t>bp</t>
+  </si>
+  <si>
+    <t>Read length</t>
+  </si>
+  <si>
+    <t>Bp</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Average Coverage</t>
+  </si>
+  <si>
+    <t>Minimum Coverage</t>
+  </si>
+  <si>
+    <t>Maximum Coverage</t>
   </si>
 </sst>
 </file>
@@ -901,7 +931,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="175" formatCode="0.000%"/>
+    <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -948,14 +978,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1237,16 +1265,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I280"/>
+  <dimension ref="A1:K280"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="4" width="12.44140625" customWidth="1"/>
     <col min="8" max="8" width="10.5546875" customWidth="1"/>
     <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1259,8 +1288,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K1" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1309,7 @@
         <v>283</v>
       </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="5">
+      <c r="H2" s="2">
         <f>AVERAGE(D2:D280)</f>
         <v>152.29964157706081</v>
       </c>
@@ -1285,8 +1317,12 @@
         <f>_xlfn.STDEV.S(D2:D300)/SQRT(COUNT(D2:D300))</f>
         <v>2.3504992180154964</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K2">
+        <f>D2*10^6*$H$9/$H$7</f>
+        <v>39.866727941176471</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1302,16 +1338,20 @@
       <c r="F3" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="1">
         <f>AVERAGE(C2:C300)</f>
         <v>0.34383512544802819</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="4">
         <f>_xlfn.STDEV.S(C2:C301)/SQRT(COUNT(C2:C301))</f>
         <v>1.2795911637945203E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="0">D3*10^6*$H$9/$H$7</f>
+        <v>39.866727941176471</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1327,16 +1367,20 @@
       <c r="F4" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="1">
         <f>AVERAGE(B3:B301)</f>
         <v>0.3636079136690647</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <f>_xlfn.STDEV.S(B2:B302)/SQRT(COUNT(B2:B302))</f>
         <v>2.6937292978209196E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>38.143382352941174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1349,8 +1393,12 @@
       <c r="D5">
         <v>182.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>41.865808823529413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1363,8 +1411,21 @@
       <c r="D6">
         <v>182.2</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F6" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H6">
+        <v>652.79999999999995</v>
+      </c>
+      <c r="I6" t="s">
+        <v>288</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>41.865808823529413</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1377,8 +1438,19 @@
       <c r="D7">
         <v>130.9</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <f>H6*10^6</f>
+        <v>652800000</v>
+      </c>
+      <c r="I7" t="s">
+        <v>291</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>30.078125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1391,8 +1463,12 @@
       <c r="D8">
         <v>130.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>30.078125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1405,8 +1481,21 @@
       <c r="D9">
         <v>142.19999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F9" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H9">
+        <v>150</v>
+      </c>
+      <c r="I9" t="s">
+        <v>289</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>32.674632352941174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1419,8 +1508,12 @@
       <c r="D10">
         <v>142.19999999999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>32.674632352941174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1433,8 +1526,22 @@
       <c r="D11">
         <v>100.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F11" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H11" s="2">
+        <f>AVERAGE(K2:K280)</f>
+        <v>34.99532205355262</v>
+      </c>
+      <c r="I11" t="s">
+        <v>292</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>23.000919117647058</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1447,8 +1554,22 @@
       <c r="D12">
         <v>100.1</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F12" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H12">
+        <f>MIN(K2:K280)</f>
+        <v>17.991727941176471</v>
+      </c>
+      <c r="I12" t="s">
+        <v>292</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>23.000919117647058</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1461,8 +1582,22 @@
       <c r="D13">
         <v>142</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F13" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="H13">
+        <f>MAX(K2:K280)</f>
+        <v>60.9375</v>
+      </c>
+      <c r="I13" t="s">
+        <v>292</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>32.628676470588232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1475,8 +1610,12 @@
       <c r="D14">
         <v>142</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>32.628676470588232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1489,8 +1628,12 @@
       <c r="D15">
         <v>182.7</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>41.980698529411768</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1503,8 +1646,12 @@
       <c r="D16">
         <v>182.7</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>41.980698529411768</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1517,8 +1664,12 @@
       <c r="D17">
         <v>190.8</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>43.841911764705884</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1531,8 +1682,12 @@
       <c r="D18">
         <v>190.8</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>43.841911764705884</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1545,8 +1700,12 @@
       <c r="D19">
         <v>138.30000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>31.778492647058822</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1559,8 +1718,12 @@
       <c r="D20">
         <v>138.30000000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>31.778492647058822</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1573,8 +1736,12 @@
       <c r="D21">
         <v>148.6</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>34.145220588235297</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1587,8 +1754,12 @@
       <c r="D22">
         <v>148.6</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>34.145220588235297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1601,8 +1772,12 @@
       <c r="D23">
         <v>123.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>28.377757352941178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1615,8 +1790,12 @@
       <c r="D24">
         <v>123.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>28.377757352941178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1629,8 +1808,12 @@
       <c r="D25">
         <v>123.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>28.377757352941178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1643,8 +1826,12 @@
       <c r="D26">
         <v>123.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>28.377757352941178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1657,8 +1844,12 @@
       <c r="D27">
         <v>107.2</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>24.632352941176471</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1671,8 +1862,12 @@
       <c r="D28">
         <v>107.2</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>24.632352941176471</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1685,8 +1880,12 @@
       <c r="D29">
         <v>161.69999999999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>37.155330882352942</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -1699,8 +1898,12 @@
       <c r="D30">
         <v>161.69999999999999</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K30">
+        <f>D30*10^6*$H$9/$H$7</f>
+        <v>37.155330882352942</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -1713,8 +1916,12 @@
       <c r="D31">
         <v>190</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K31">
+        <f t="shared" si="0"/>
+        <v>43.658088235294116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -1727,8 +1934,12 @@
       <c r="D32">
         <v>190</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>43.658088235294116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -1741,8 +1952,12 @@
       <c r="D33">
         <v>117.6</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K33">
+        <f t="shared" si="0"/>
+        <v>27.022058823529413</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -1755,8 +1970,12 @@
       <c r="D34">
         <v>117.6</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>27.022058823529413</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1769,8 +1988,12 @@
       <c r="D35">
         <v>155.6</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K35">
+        <f t="shared" si="0"/>
+        <v>35.753676470588232</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -1783,8 +2006,12 @@
       <c r="D36">
         <v>155.6</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K36">
+        <f t="shared" si="0"/>
+        <v>35.753676470588232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1797,8 +2024,12 @@
       <c r="D37">
         <v>87.6</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K37">
+        <f t="shared" si="0"/>
+        <v>20.128676470588236</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1811,8 +2042,12 @@
       <c r="D38">
         <v>87.6</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K38">
+        <f t="shared" si="0"/>
+        <v>20.128676470588236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1825,8 +2060,12 @@
       <c r="D39">
         <v>136.9</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K39">
+        <f t="shared" si="0"/>
+        <v>31.456801470588236</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1839,8 +2078,12 @@
       <c r="D40">
         <v>136.9</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K40">
+        <f t="shared" si="0"/>
+        <v>31.456801470588236</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -1853,8 +2096,12 @@
       <c r="D41">
         <v>117</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K41">
+        <f t="shared" si="0"/>
+        <v>26.884191176470587</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1867,8 +2114,12 @@
       <c r="D42">
         <v>117</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K42">
+        <f t="shared" si="0"/>
+        <v>26.884191176470587</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1881,8 +2132,12 @@
       <c r="D43">
         <v>124.3</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K43">
+        <f t="shared" si="0"/>
+        <v>28.561580882352942</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1895,8 +2150,12 @@
       <c r="D44">
         <v>124.3</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K44">
+        <f t="shared" si="0"/>
+        <v>28.561580882352942</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -1909,8 +2168,12 @@
       <c r="D45">
         <v>161.9</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K45">
+        <f t="shared" si="0"/>
+        <v>37.201286764705884</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -1923,8 +2186,12 @@
       <c r="D46">
         <v>161.9</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K46">
+        <f t="shared" si="0"/>
+        <v>37.201286764705884</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -1937,8 +2204,12 @@
       <c r="D47">
         <v>145.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K47">
+        <f t="shared" si="0"/>
+        <v>33.340992647058826</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1951,8 +2222,12 @@
       <c r="D48">
         <v>145.1</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K48">
+        <f t="shared" si="0"/>
+        <v>33.340992647058826</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1965,8 +2240,12 @@
       <c r="D49">
         <v>179.9</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K49">
+        <f t="shared" si="0"/>
+        <v>41.337316176470587</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -1979,8 +2258,12 @@
       <c r="D50">
         <v>179.9</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K50">
+        <f>D50*10^6*$H$9/$H$7</f>
+        <v>41.337316176470587</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1993,8 +2276,12 @@
       <c r="D51">
         <v>191.3</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K51">
+        <f t="shared" si="0"/>
+        <v>43.956801470588232</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -2007,8 +2294,12 @@
       <c r="D52">
         <v>191.3</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K52">
+        <f t="shared" si="0"/>
+        <v>43.956801470588232</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -2021,8 +2312,12 @@
       <c r="D53">
         <v>147.9</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K53">
+        <f t="shared" si="0"/>
+        <v>33.984375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -2035,8 +2330,12 @@
       <c r="D54">
         <v>147.9</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K54">
+        <f t="shared" si="0"/>
+        <v>33.984375</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -2049,8 +2348,12 @@
       <c r="D55">
         <v>189.9</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K55">
+        <f t="shared" si="0"/>
+        <v>43.635110294117645</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -2063,8 +2366,12 @@
       <c r="D56">
         <v>189.9</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K56">
+        <f t="shared" si="0"/>
+        <v>43.635110294117645</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -2077,8 +2384,12 @@
       <c r="D57">
         <v>160.6</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K57">
+        <f t="shared" si="0"/>
+        <v>36.902573529411768</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -2091,8 +2402,12 @@
       <c r="D58">
         <v>160.6</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K58">
+        <f t="shared" si="0"/>
+        <v>36.902573529411768</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -2105,8 +2420,12 @@
       <c r="D59">
         <v>131.1</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K59">
+        <f t="shared" si="0"/>
+        <v>30.124080882352942</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -2119,8 +2438,12 @@
       <c r="D60">
         <v>131.1</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K60">
+        <f t="shared" si="0"/>
+        <v>30.124080882352942</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -2133,8 +2456,12 @@
       <c r="D61">
         <v>99.8</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K61">
+        <f t="shared" si="0"/>
+        <v>22.931985294117649</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -2147,8 +2474,12 @@
       <c r="D62">
         <v>99.8</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K62">
+        <f t="shared" si="0"/>
+        <v>22.931985294117649</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -2161,8 +2492,12 @@
       <c r="D63">
         <v>142.30000000000001</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K63">
+        <f t="shared" si="0"/>
+        <v>32.697610294117645</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -2175,8 +2510,12 @@
       <c r="D64">
         <v>142.30000000000001</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K64">
+        <f t="shared" si="0"/>
+        <v>32.697610294117645</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -2189,8 +2528,12 @@
       <c r="D65">
         <v>219.2</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K65">
+        <f t="shared" si="0"/>
+        <v>50.367647058823529</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -2203,8 +2546,12 @@
       <c r="D66">
         <v>219.2</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K66">
+        <f t="shared" si="0"/>
+        <v>50.367647058823529</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -2217,8 +2564,12 @@
       <c r="D67">
         <v>149.19999999999999</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K67">
+        <f t="shared" ref="K67:K130" si="1">D67*10^6*$H$9/$H$7</f>
+        <v>34.283088235294116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -2231,8 +2582,12 @@
       <c r="D68">
         <v>149.19999999999999</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K68">
+        <f t="shared" si="1"/>
+        <v>34.283088235294116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -2245,8 +2600,12 @@
       <c r="D69">
         <v>173.1</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K69">
+        <f t="shared" si="1"/>
+        <v>39.774816176470587</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -2259,8 +2618,12 @@
       <c r="D70">
         <v>173.1</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K70">
+        <f t="shared" si="1"/>
+        <v>39.774816176470587</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -2273,8 +2636,12 @@
       <c r="D71">
         <v>111.9</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K71">
+        <f t="shared" si="1"/>
+        <v>25.712316176470587</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -2287,8 +2654,12 @@
       <c r="D72">
         <v>111.9</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K72">
+        <f t="shared" si="1"/>
+        <v>25.712316176470587</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -2301,8 +2672,12 @@
       <c r="D73">
         <v>157.69999999999999</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K73">
+        <f t="shared" si="1"/>
+        <v>36.236213235294116</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -2315,8 +2690,12 @@
       <c r="D74">
         <v>157.69999999999999</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K74">
+        <f t="shared" si="1"/>
+        <v>36.236213235294116</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -2329,8 +2708,12 @@
       <c r="D75">
         <v>188.8</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K75">
+        <f t="shared" si="1"/>
+        <v>43.382352941176471</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -2343,8 +2726,12 @@
       <c r="D76">
         <v>188.8</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K76">
+        <f t="shared" si="1"/>
+        <v>43.382352941176471</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -2357,8 +2744,12 @@
       <c r="D77">
         <v>187.8</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K77">
+        <f t="shared" si="1"/>
+        <v>43.152573529411768</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -2371,8 +2762,12 @@
       <c r="D78">
         <v>187.8</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K78">
+        <f t="shared" si="1"/>
+        <v>43.152573529411768</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -2385,8 +2780,12 @@
       <c r="D79">
         <v>230.9</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K79">
+        <f t="shared" si="1"/>
+        <v>53.056066176470587</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -2399,8 +2798,12 @@
       <c r="D80">
         <v>230.9</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K80">
+        <f t="shared" si="1"/>
+        <v>53.056066176470587</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2413,8 +2816,12 @@
       <c r="D81">
         <v>222.4</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K81">
+        <f t="shared" si="1"/>
+        <v>51.102941176470587</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -2427,8 +2834,12 @@
       <c r="D82">
         <v>222.4</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K82">
+        <f t="shared" si="1"/>
+        <v>51.102941176470587</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -2441,8 +2852,12 @@
       <c r="D83">
         <v>217.2</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K83">
+        <f t="shared" si="1"/>
+        <v>49.908088235294116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -2455,8 +2870,12 @@
       <c r="D84">
         <v>217.2</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K84">
+        <f t="shared" si="1"/>
+        <v>49.908088235294116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -2469,8 +2888,12 @@
       <c r="D85">
         <v>163.30000000000001</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K85">
+        <f t="shared" si="1"/>
+        <v>37.522977941176471</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -2483,8 +2906,12 @@
       <c r="D86">
         <v>163.30000000000001</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K86">
+        <f t="shared" si="1"/>
+        <v>37.522977941176471</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -2497,8 +2924,12 @@
       <c r="D87">
         <v>186.8</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K87">
+        <f t="shared" si="1"/>
+        <v>42.922794117647058</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -2511,8 +2942,12 @@
       <c r="D88">
         <v>186.8</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K88">
+        <f t="shared" si="1"/>
+        <v>42.922794117647058</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -2525,8 +2960,12 @@
       <c r="D89">
         <v>167.2</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K89">
+        <f t="shared" si="1"/>
+        <v>38.419117647058826</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -2539,8 +2978,12 @@
       <c r="D90">
         <v>167.2</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K90">
+        <f t="shared" si="1"/>
+        <v>38.419117647058826</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -2553,8 +2996,12 @@
       <c r="D91">
         <v>138.19999999999999</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K91">
+        <f t="shared" si="1"/>
+        <v>31.755514705882351</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -2567,8 +3014,12 @@
       <c r="D92">
         <v>138.19999999999999</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K92">
+        <f t="shared" si="1"/>
+        <v>31.755514705882351</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -2581,8 +3032,12 @@
       <c r="D93">
         <v>130.6</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K93">
+        <f t="shared" si="1"/>
+        <v>30.009191176470587</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -2595,8 +3050,12 @@
       <c r="D94">
         <v>130.6</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K94">
+        <f t="shared" si="1"/>
+        <v>30.009191176470587</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -2609,8 +3068,12 @@
       <c r="D95">
         <v>184.8</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K95">
+        <f t="shared" si="1"/>
+        <v>42.463235294117645</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -2623,8 +3086,12 @@
       <c r="D96">
         <v>184.8</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K96">
+        <f t="shared" si="1"/>
+        <v>42.463235294117645</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -2637,8 +3104,12 @@
       <c r="D97">
         <v>143.4</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K97">
+        <f t="shared" si="1"/>
+        <v>32.950367647058826</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -2651,8 +3122,12 @@
       <c r="D98">
         <v>143.4</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K98">
+        <f t="shared" si="1"/>
+        <v>32.950367647058826</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>101</v>
       </c>
@@ -2665,8 +3140,12 @@
       <c r="D99">
         <v>260</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K99">
+        <f t="shared" si="1"/>
+        <v>59.742647058823529</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>102</v>
       </c>
@@ -2679,8 +3158,12 @@
       <c r="D100">
         <v>260</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K100">
+        <f t="shared" si="1"/>
+        <v>59.742647058823529</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>103</v>
       </c>
@@ -2693,8 +3176,12 @@
       <c r="D101">
         <v>132</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K101">
+        <f t="shared" si="1"/>
+        <v>30.330882352941178</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>104</v>
       </c>
@@ -2707,8 +3194,12 @@
       <c r="D102">
         <v>132</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K102">
+        <f t="shared" si="1"/>
+        <v>30.330882352941178</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -2721,8 +3212,12 @@
       <c r="D103">
         <v>144.4</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K103">
+        <f t="shared" si="1"/>
+        <v>33.180147058823529</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>106</v>
       </c>
@@ -2735,8 +3230,12 @@
       <c r="D104">
         <v>144.4</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K104">
+        <f t="shared" si="1"/>
+        <v>33.180147058823529</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>107</v>
       </c>
@@ -2749,8 +3248,12 @@
       <c r="D105">
         <v>130.9</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K105">
+        <f t="shared" si="1"/>
+        <v>30.078125</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>108</v>
       </c>
@@ -2763,8 +3266,12 @@
       <c r="D106">
         <v>130.9</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K106">
+        <f t="shared" si="1"/>
+        <v>30.078125</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>109</v>
       </c>
@@ -2777,8 +3284,12 @@
       <c r="D107">
         <v>134.5</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K107">
+        <f t="shared" si="1"/>
+        <v>30.905330882352942</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>110</v>
       </c>
@@ -2791,8 +3302,12 @@
       <c r="D108">
         <v>134.5</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K108">
+        <f t="shared" si="1"/>
+        <v>30.905330882352942</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>111</v>
       </c>
@@ -2805,8 +3320,12 @@
       <c r="D109">
         <v>115.5</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K109">
+        <f t="shared" si="1"/>
+        <v>26.539522058823529</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>112</v>
       </c>
@@ -2819,8 +3338,12 @@
       <c r="D110">
         <v>115.5</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K110">
+        <f t="shared" si="1"/>
+        <v>26.539522058823529</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>113</v>
       </c>
@@ -2833,8 +3356,12 @@
       <c r="D111">
         <v>122</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K111">
+        <f t="shared" si="1"/>
+        <v>28.033088235294116</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -2847,8 +3374,12 @@
       <c r="D112">
         <v>122</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K112">
+        <f t="shared" si="1"/>
+        <v>28.033088235294116</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -2861,8 +3392,12 @@
       <c r="D113">
         <v>141.4</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K113">
+        <f t="shared" si="1"/>
+        <v>32.490808823529413</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -2875,8 +3410,12 @@
       <c r="D114">
         <v>141.4</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K114">
+        <f t="shared" si="1"/>
+        <v>32.490808823529413</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -2889,8 +3428,12 @@
       <c r="D115">
         <v>103.3</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K115">
+        <f t="shared" si="1"/>
+        <v>23.736213235294116</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -2903,8 +3446,12 @@
       <c r="D116">
         <v>103.3</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K116">
+        <f t="shared" si="1"/>
+        <v>23.736213235294116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>119</v>
       </c>
@@ -2917,8 +3464,12 @@
       <c r="D117">
         <v>185.9</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K117">
+        <f t="shared" si="1"/>
+        <v>42.715992647058826</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -2931,8 +3482,12 @@
       <c r="D118">
         <v>185.9</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K118">
+        <f t="shared" si="1"/>
+        <v>42.715992647058826</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -2945,8 +3500,12 @@
       <c r="D119">
         <v>164.8</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K119">
+        <f t="shared" si="1"/>
+        <v>37.867647058823529</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>122</v>
       </c>
@@ -2959,8 +3518,12 @@
       <c r="D120">
         <v>164.8</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K120">
+        <f t="shared" si="1"/>
+        <v>37.867647058823529</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>123</v>
       </c>
@@ -2973,8 +3536,12 @@
       <c r="D121">
         <v>125.1</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K121">
+        <f t="shared" si="1"/>
+        <v>28.745404411764707</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>124</v>
       </c>
@@ -2987,8 +3554,12 @@
       <c r="D122">
         <v>125.1</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K122">
+        <f t="shared" si="1"/>
+        <v>28.745404411764707</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>125</v>
       </c>
@@ -3001,8 +3572,12 @@
       <c r="D123">
         <v>132.4</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K123">
+        <f t="shared" si="1"/>
+        <v>30.422794117647058</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>126</v>
       </c>
@@ -3015,8 +3590,12 @@
       <c r="D124">
         <v>132.4</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K124">
+        <f t="shared" si="1"/>
+        <v>30.422794117647058</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>127</v>
       </c>
@@ -3029,8 +3608,12 @@
       <c r="D125">
         <v>220.8</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K125">
+        <f t="shared" si="1"/>
+        <v>50.735294117647058</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>128</v>
       </c>
@@ -3043,8 +3626,12 @@
       <c r="D126">
         <v>220.8</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K126">
+        <f t="shared" si="1"/>
+        <v>50.735294117647058</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>129</v>
       </c>
@@ -3057,8 +3644,12 @@
       <c r="D127">
         <v>186.7</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K127">
+        <f t="shared" si="1"/>
+        <v>42.899816176470587</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>130</v>
       </c>
@@ -3071,8 +3662,12 @@
       <c r="D128">
         <v>186.7</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K128">
+        <f t="shared" si="1"/>
+        <v>42.899816176470587</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>131</v>
       </c>
@@ -3085,8 +3680,12 @@
       <c r="D129">
         <v>113.8</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K129">
+        <f t="shared" si="1"/>
+        <v>26.148897058823529</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>132</v>
       </c>
@@ -3099,8 +3698,12 @@
       <c r="D130">
         <v>113.8</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K130">
+        <f t="shared" si="1"/>
+        <v>26.148897058823529</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>133</v>
       </c>
@@ -3113,8 +3716,12 @@
       <c r="D131">
         <v>105</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K131">
+        <f t="shared" ref="K131:K194" si="2">D131*10^6*$H$9/$H$7</f>
+        <v>24.126838235294116</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>134</v>
       </c>
@@ -3127,8 +3734,12 @@
       <c r="D132">
         <v>105</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K132">
+        <f t="shared" si="2"/>
+        <v>24.126838235294116</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>135</v>
       </c>
@@ -3141,8 +3752,12 @@
       <c r="D133">
         <v>128.5</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K133">
+        <f t="shared" si="2"/>
+        <v>29.526654411764707</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>136</v>
       </c>
@@ -3155,8 +3770,12 @@
       <c r="D134">
         <v>128.5</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K134">
+        <f t="shared" si="2"/>
+        <v>29.526654411764707</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>137</v>
       </c>
@@ -3169,8 +3788,12 @@
       <c r="D135">
         <v>118.1</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K135">
+        <f t="shared" si="2"/>
+        <v>27.136948529411764</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>138</v>
       </c>
@@ -3183,8 +3806,12 @@
       <c r="D136">
         <v>118.1</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K136">
+        <f t="shared" si="2"/>
+        <v>27.136948529411764</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -3197,8 +3824,12 @@
       <c r="D137">
         <v>169.2</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K137">
+        <f t="shared" si="2"/>
+        <v>38.878676470588232</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -3211,8 +3842,12 @@
       <c r="D138">
         <v>169.2</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K138">
+        <f t="shared" si="2"/>
+        <v>38.878676470588232</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>141</v>
       </c>
@@ -3225,8 +3860,12 @@
       <c r="D139">
         <v>93.2</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K139">
+        <f t="shared" si="2"/>
+        <v>21.415441176470587</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -3239,8 +3878,12 @@
       <c r="D140">
         <v>93.2</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K140">
+        <f t="shared" si="2"/>
+        <v>21.415441176470587</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>143</v>
       </c>
@@ -3253,8 +3896,12 @@
       <c r="D141">
         <v>226.5</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K141">
+        <f t="shared" si="2"/>
+        <v>52.045036764705884</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>144</v>
       </c>
@@ -3267,8 +3914,12 @@
       <c r="D142">
         <v>226.5</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K142">
+        <f t="shared" si="2"/>
+        <v>52.045036764705884</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>145</v>
       </c>
@@ -3281,8 +3932,12 @@
       <c r="D143">
         <v>102.5</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K143">
+        <f t="shared" si="2"/>
+        <v>23.552389705882351</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>146</v>
       </c>
@@ -3295,8 +3950,12 @@
       <c r="D144">
         <v>102.5</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K144">
+        <f t="shared" si="2"/>
+        <v>23.552389705882351</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>147</v>
       </c>
@@ -3309,8 +3968,12 @@
       <c r="D145">
         <v>127.4</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K145">
+        <f t="shared" si="2"/>
+        <v>29.273897058823529</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>148</v>
       </c>
@@ -3323,8 +3986,12 @@
       <c r="D146">
         <v>127.4</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K146">
+        <f t="shared" si="2"/>
+        <v>29.273897058823529</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>149</v>
       </c>
@@ -3337,8 +4004,12 @@
       <c r="D147">
         <v>147.80000000000001</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K147">
+        <f t="shared" si="2"/>
+        <v>33.961397058823529</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -3351,8 +4022,12 @@
       <c r="D148">
         <v>147.80000000000001</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K148">
+        <f t="shared" si="2"/>
+        <v>33.961397058823529</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>151</v>
       </c>
@@ -3365,8 +4040,12 @@
       <c r="D149">
         <v>108.5</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K149">
+        <f t="shared" si="2"/>
+        <v>24.931066176470587</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>152</v>
       </c>
@@ -3379,8 +4058,12 @@
       <c r="D150">
         <v>108.5</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K150">
+        <f t="shared" si="2"/>
+        <v>24.931066176470587</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>153</v>
       </c>
@@ -3393,8 +4076,12 @@
       <c r="D151">
         <v>179.6</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K151">
+        <f t="shared" si="2"/>
+        <v>41.268382352941174</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>154</v>
       </c>
@@ -3407,8 +4094,12 @@
       <c r="D152">
         <v>179.6</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K152">
+        <f t="shared" si="2"/>
+        <v>41.268382352941174</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>155</v>
       </c>
@@ -3421,8 +4112,12 @@
       <c r="D153">
         <v>129.5</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K153">
+        <f t="shared" si="2"/>
+        <v>29.756433823529413</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>156</v>
       </c>
@@ -3435,8 +4130,12 @@
       <c r="D154">
         <v>129.5</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K154">
+        <f t="shared" si="2"/>
+        <v>29.756433823529413</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>157</v>
       </c>
@@ -3449,8 +4148,12 @@
       <c r="D155">
         <v>98.4</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K155">
+        <f t="shared" si="2"/>
+        <v>22.610294117647058</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>158</v>
       </c>
@@ -3463,8 +4166,12 @@
       <c r="D156">
         <v>98.4</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K156">
+        <f t="shared" si="2"/>
+        <v>22.610294117647058</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>159</v>
       </c>
@@ -3477,8 +4184,12 @@
       <c r="D157">
         <v>176.4</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K157">
+        <f t="shared" si="2"/>
+        <v>40.533088235294116</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>160</v>
       </c>
@@ -3491,8 +4202,12 @@
       <c r="D158">
         <v>176.4</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K158">
+        <f t="shared" si="2"/>
+        <v>40.533088235294116</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>161</v>
       </c>
@@ -3505,8 +4220,12 @@
       <c r="D159">
         <v>106.1</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K159">
+        <f t="shared" si="2"/>
+        <v>24.379595588235293</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -3519,8 +4238,12 @@
       <c r="D160">
         <v>106.1</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K160">
+        <f t="shared" si="2"/>
+        <v>24.379595588235293</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>163</v>
       </c>
@@ -3533,8 +4256,12 @@
       <c r="D161">
         <v>151.30000000000001</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K161">
+        <f t="shared" si="2"/>
+        <v>34.765625</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>164</v>
       </c>
@@ -3547,8 +4274,12 @@
       <c r="D162">
         <v>151.30000000000001</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K162">
+        <f t="shared" si="2"/>
+        <v>34.765625</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>165</v>
       </c>
@@ -3561,8 +4292,12 @@
       <c r="D163">
         <v>116.1</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K163">
+        <f t="shared" si="2"/>
+        <v>26.677389705882351</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>166</v>
       </c>
@@ -3575,8 +4310,12 @@
       <c r="D164">
         <v>116.1</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K164">
+        <f t="shared" si="2"/>
+        <v>26.677389705882351</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>167</v>
       </c>
@@ -3589,8 +4328,12 @@
       <c r="D165">
         <v>140.9</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K165">
+        <f t="shared" si="2"/>
+        <v>32.375919117647058</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>168</v>
       </c>
@@ -3603,8 +4346,12 @@
       <c r="D166">
         <v>140.9</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K166">
+        <f t="shared" si="2"/>
+        <v>32.375919117647058</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>169</v>
       </c>
@@ -3617,8 +4364,12 @@
       <c r="D167">
         <v>149</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K167">
+        <f t="shared" si="2"/>
+        <v>34.237132352941174</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>170</v>
       </c>
@@ -3631,8 +4382,12 @@
       <c r="D168">
         <v>149</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K168">
+        <f t="shared" si="2"/>
+        <v>34.237132352941174</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>171</v>
       </c>
@@ -3645,8 +4400,12 @@
       <c r="D169">
         <v>124.8</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K169">
+        <f t="shared" si="2"/>
+        <v>28.676470588235293</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>172</v>
       </c>
@@ -3659,8 +4418,12 @@
       <c r="D170">
         <v>124.8</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K170">
+        <f t="shared" si="2"/>
+        <v>28.676470588235293</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>173</v>
       </c>
@@ -3673,8 +4436,12 @@
       <c r="D171">
         <v>174.6</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K171">
+        <f t="shared" si="2"/>
+        <v>40.119485294117645</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>174</v>
       </c>
@@ -3687,8 +4454,12 @@
       <c r="D172">
         <v>174.6</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K172">
+        <f t="shared" si="2"/>
+        <v>40.119485294117645</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>175</v>
       </c>
@@ -3701,8 +4472,12 @@
       <c r="D173">
         <v>130</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K173">
+        <f t="shared" si="2"/>
+        <v>29.871323529411764</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>176</v>
       </c>
@@ -3715,8 +4490,12 @@
       <c r="D174">
         <v>130</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K174">
+        <f t="shared" si="2"/>
+        <v>29.871323529411764</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>177</v>
       </c>
@@ -3729,8 +4508,12 @@
       <c r="D175">
         <v>181.7</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K175">
+        <f t="shared" si="2"/>
+        <v>41.750919117647058</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>178</v>
       </c>
@@ -3743,8 +4526,12 @@
       <c r="D176">
         <v>181.7</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K176">
+        <f t="shared" si="2"/>
+        <v>41.750919117647058</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>179</v>
       </c>
@@ -3757,8 +4544,12 @@
       <c r="D177">
         <v>117.9</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K177">
+        <f t="shared" si="2"/>
+        <v>27.090992647058822</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>180</v>
       </c>
@@ -3771,8 +4562,12 @@
       <c r="D178">
         <v>117.9</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K178">
+        <f t="shared" si="2"/>
+        <v>27.090992647058822</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>181</v>
       </c>
@@ -3785,8 +4580,12 @@
       <c r="D179">
         <v>118.1</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K179">
+        <f t="shared" si="2"/>
+        <v>27.136948529411764</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>182</v>
       </c>
@@ -3799,8 +4598,12 @@
       <c r="D180">
         <v>118.1</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K180">
+        <f t="shared" si="2"/>
+        <v>27.136948529411764</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>183</v>
       </c>
@@ -3813,8 +4616,12 @@
       <c r="D181">
         <v>131</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K181">
+        <f t="shared" si="2"/>
+        <v>30.101102941176471</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>184</v>
       </c>
@@ -3827,8 +4634,12 @@
       <c r="D182">
         <v>131</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K182">
+        <f t="shared" si="2"/>
+        <v>30.101102941176471</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>185</v>
       </c>
@@ -3841,8 +4652,12 @@
       <c r="D183">
         <v>109</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K183">
+        <f t="shared" si="2"/>
+        <v>25.045955882352942</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>186</v>
       </c>
@@ -3855,8 +4670,12 @@
       <c r="D184">
         <v>109</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K184">
+        <f t="shared" si="2"/>
+        <v>25.045955882352942</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>187</v>
       </c>
@@ -3869,8 +4688,12 @@
       <c r="D185">
         <v>189</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K185">
+        <f t="shared" si="2"/>
+        <v>43.428308823529413</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>188</v>
       </c>
@@ -3883,8 +4706,12 @@
       <c r="D186">
         <v>189</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K186">
+        <f t="shared" si="2"/>
+        <v>43.428308823529413</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>189</v>
       </c>
@@ -3897,8 +4724,12 @@
       <c r="D187">
         <v>147.1</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K187">
+        <f t="shared" si="2"/>
+        <v>33.800551470588232</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>190</v>
       </c>
@@ -3911,8 +4742,12 @@
       <c r="D188">
         <v>147.1</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K188">
+        <f t="shared" si="2"/>
+        <v>33.800551470588232</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>191</v>
       </c>
@@ -3925,8 +4760,12 @@
       <c r="D189">
         <v>162.6</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K189">
+        <f t="shared" si="2"/>
+        <v>37.362132352941174</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>192</v>
       </c>
@@ -3939,8 +4778,12 @@
       <c r="D190">
         <v>162.6</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K190">
+        <f t="shared" si="2"/>
+        <v>37.362132352941174</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>193</v>
       </c>
@@ -3953,8 +4796,12 @@
       <c r="D191">
         <v>91.3</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K191">
+        <f t="shared" si="2"/>
+        <v>20.978860294117649</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>194</v>
       </c>
@@ -3967,8 +4814,12 @@
       <c r="D192">
         <v>91.3</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K192">
+        <f t="shared" si="2"/>
+        <v>20.978860294117649</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>195</v>
       </c>
@@ -3981,8 +4832,12 @@
       <c r="D193">
         <v>90.7</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K193">
+        <f t="shared" si="2"/>
+        <v>20.840992647058822</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>196</v>
       </c>
@@ -3995,8 +4850,12 @@
       <c r="D194">
         <v>90.7</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K194">
+        <f t="shared" si="2"/>
+        <v>20.840992647058822</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>197</v>
       </c>
@@ -4009,8 +4868,12 @@
       <c r="D195">
         <v>114.8</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K195">
+        <f t="shared" ref="K195:K258" si="3">D195*10^6*$H$9/$H$7</f>
+        <v>26.378676470588236</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>198</v>
       </c>
@@ -4023,8 +4886,12 @@
       <c r="D196">
         <v>114.8</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K196">
+        <f t="shared" si="3"/>
+        <v>26.378676470588236</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -4037,8 +4904,12 @@
       <c r="D197">
         <v>182.9</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K197">
+        <f t="shared" si="3"/>
+        <v>42.026654411764703</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>200</v>
       </c>
@@ -4051,8 +4922,12 @@
       <c r="D198">
         <v>182.9</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K198">
+        <f t="shared" si="3"/>
+        <v>42.026654411764703</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>201</v>
       </c>
@@ -4065,8 +4940,12 @@
       <c r="D199">
         <v>100.8</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K199">
+        <f t="shared" si="3"/>
+        <v>23.161764705882351</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>202</v>
       </c>
@@ -4079,8 +4958,12 @@
       <c r="D200">
         <v>100.8</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K200">
+        <f t="shared" si="3"/>
+        <v>23.161764705882351</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>203</v>
       </c>
@@ -4093,8 +4976,12 @@
       <c r="D201">
         <v>119.4</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K201">
+        <f t="shared" si="3"/>
+        <v>27.435661764705884</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>204</v>
       </c>
@@ -4107,8 +4994,12 @@
       <c r="D202">
         <v>119.4</v>
       </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K202">
+        <f t="shared" si="3"/>
+        <v>27.435661764705884</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>205</v>
       </c>
@@ -4121,8 +5012,12 @@
       <c r="D203">
         <v>163.19999999999999</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K203">
+        <f t="shared" si="3"/>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>206</v>
       </c>
@@ -4135,8 +5030,12 @@
       <c r="D204">
         <v>163.19999999999999</v>
       </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K204">
+        <f t="shared" si="3"/>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>207</v>
       </c>
@@ -4149,8 +5048,12 @@
       <c r="D205">
         <v>116.2</v>
       </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K205">
+        <f t="shared" si="3"/>
+        <v>26.700367647058822</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>208</v>
       </c>
@@ -4163,8 +5066,12 @@
       <c r="D206">
         <v>116.2</v>
       </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K206">
+        <f t="shared" si="3"/>
+        <v>26.700367647058822</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>209</v>
       </c>
@@ -4177,8 +5084,12 @@
       <c r="D207">
         <v>100.7</v>
       </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K207">
+        <f t="shared" si="3"/>
+        <v>23.138786764705884</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>210</v>
       </c>
@@ -4191,8 +5102,12 @@
       <c r="D208">
         <v>100.7</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K208">
+        <f t="shared" si="3"/>
+        <v>23.138786764705884</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>211</v>
       </c>
@@ -4205,8 +5120,12 @@
       <c r="D209">
         <v>88.2</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K209">
+        <f t="shared" si="3"/>
+        <v>20.266544117647058</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>212</v>
       </c>
@@ -4219,8 +5138,12 @@
       <c r="D210">
         <v>88.2</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K210">
+        <f t="shared" si="3"/>
+        <v>20.266544117647058</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>213</v>
       </c>
@@ -4233,8 +5156,12 @@
       <c r="D211">
         <v>179.5</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K211">
+        <f t="shared" si="3"/>
+        <v>41.245404411764703</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>214</v>
       </c>
@@ -4247,8 +5174,12 @@
       <c r="D212">
         <v>179.5</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K212">
+        <f t="shared" si="3"/>
+        <v>41.245404411764703</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>215</v>
       </c>
@@ -4261,8 +5192,12 @@
       <c r="D213">
         <v>131</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K213">
+        <f t="shared" si="3"/>
+        <v>30.101102941176471</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>216</v>
       </c>
@@ -4275,8 +5210,12 @@
       <c r="D214">
         <v>131</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K214">
+        <f t="shared" si="3"/>
+        <v>30.101102941176471</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>217</v>
       </c>
@@ -4289,8 +5228,12 @@
       <c r="D215">
         <v>160.30000000000001</v>
       </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K215">
+        <f t="shared" si="3"/>
+        <v>36.833639705882355</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>218</v>
       </c>
@@ -4303,8 +5246,12 @@
       <c r="D216">
         <v>160.30000000000001</v>
       </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K216">
+        <f t="shared" si="3"/>
+        <v>36.833639705882355</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>219</v>
       </c>
@@ -4317,8 +5264,12 @@
       <c r="D217">
         <v>141.5</v>
       </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K217">
+        <f t="shared" si="3"/>
+        <v>32.513786764705884</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>220</v>
       </c>
@@ -4331,8 +5282,12 @@
       <c r="D218">
         <v>141.5</v>
       </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K218">
+        <f t="shared" si="3"/>
+        <v>32.513786764705884</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>221</v>
       </c>
@@ -4345,8 +5300,12 @@
       <c r="D219">
         <v>191.9</v>
       </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K219">
+        <f t="shared" si="3"/>
+        <v>44.094669117647058</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>222</v>
       </c>
@@ -4359,8 +5318,12 @@
       <c r="D220">
         <v>191.9</v>
       </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K220">
+        <f t="shared" si="3"/>
+        <v>44.094669117647058</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>223</v>
       </c>
@@ -4373,8 +5336,12 @@
       <c r="D221">
         <v>112.4</v>
       </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K221">
+        <f t="shared" si="3"/>
+        <v>25.827205882352942</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>224</v>
       </c>
@@ -4387,8 +5354,12 @@
       <c r="D222">
         <v>112.4</v>
       </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K222">
+        <f t="shared" si="3"/>
+        <v>25.827205882352942</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>225</v>
       </c>
@@ -4401,8 +5372,12 @@
       <c r="D223">
         <v>156.6</v>
       </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K223">
+        <f t="shared" si="3"/>
+        <v>35.983455882352942</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>226</v>
       </c>
@@ -4415,8 +5390,12 @@
       <c r="D224">
         <v>156.6</v>
       </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K224">
+        <f t="shared" si="3"/>
+        <v>35.983455882352942</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>227</v>
       </c>
@@ -4429,8 +5408,12 @@
       <c r="D225">
         <v>142.19999999999999</v>
       </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K225">
+        <f t="shared" si="3"/>
+        <v>32.674632352941174</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>228</v>
       </c>
@@ -4443,8 +5426,12 @@
       <c r="D226">
         <v>142.19999999999999</v>
       </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K226">
+        <f t="shared" si="3"/>
+        <v>32.674632352941174</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>229</v>
       </c>
@@ -4457,8 +5444,12 @@
       <c r="D227">
         <v>78.3</v>
       </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K227">
+        <f t="shared" si="3"/>
+        <v>17.991727941176471</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>230</v>
       </c>
@@ -4471,8 +5462,12 @@
       <c r="D228">
         <v>78.3</v>
       </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K228">
+        <f t="shared" si="3"/>
+        <v>17.991727941176471</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>231</v>
       </c>
@@ -4485,8 +5480,12 @@
       <c r="D229">
         <v>141.4</v>
       </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K229">
+        <f t="shared" si="3"/>
+        <v>32.490808823529413</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>232</v>
       </c>
@@ -4499,8 +5498,12 @@
       <c r="D230">
         <v>141.4</v>
       </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K230">
+        <f t="shared" si="3"/>
+        <v>32.490808823529413</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>233</v>
       </c>
@@ -4513,8 +5516,12 @@
       <c r="D231">
         <v>139.69999999999999</v>
       </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K231">
+        <f t="shared" si="3"/>
+        <v>32.100183823529413</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>234</v>
       </c>
@@ -4527,8 +5534,12 @@
       <c r="D232">
         <v>139.69999999999999</v>
       </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K232">
+        <f t="shared" si="3"/>
+        <v>32.100183823529413</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>235</v>
       </c>
@@ -4541,8 +5552,12 @@
       <c r="D233">
         <v>188.1</v>
       </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K233">
+        <f t="shared" si="3"/>
+        <v>43.221507352941174</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>236</v>
       </c>
@@ -4555,8 +5570,12 @@
       <c r="D234">
         <v>188.1</v>
       </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K234">
+        <f t="shared" si="3"/>
+        <v>43.221507352941174</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>237</v>
       </c>
@@ -4569,8 +5588,12 @@
       <c r="D235">
         <v>101.1</v>
       </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K235">
+        <f t="shared" si="3"/>
+        <v>23.230698529411764</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>238</v>
       </c>
@@ -4583,8 +5606,12 @@
       <c r="D236">
         <v>101.1</v>
       </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K236">
+        <f t="shared" si="3"/>
+        <v>23.230698529411764</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>239</v>
       </c>
@@ -4597,8 +5624,12 @@
       <c r="D237">
         <v>212.7</v>
       </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K237">
+        <f t="shared" si="3"/>
+        <v>48.874080882352942</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>240</v>
       </c>
@@ -4611,8 +5642,12 @@
       <c r="D238">
         <v>212.7</v>
       </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K238">
+        <f t="shared" si="3"/>
+        <v>48.874080882352942</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>241</v>
       </c>
@@ -4625,8 +5660,12 @@
       <c r="D239">
         <v>168.2</v>
       </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K239">
+        <f t="shared" si="3"/>
+        <v>38.648897058823529</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>242</v>
       </c>
@@ -4639,8 +5678,12 @@
       <c r="D240">
         <v>168.2</v>
       </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K240">
+        <f t="shared" si="3"/>
+        <v>38.648897058823529</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>243</v>
       </c>
@@ -4653,8 +5696,12 @@
       <c r="D241">
         <v>146.30000000000001</v>
       </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K241">
+        <f t="shared" si="3"/>
+        <v>33.616727941176471</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>244</v>
       </c>
@@ -4667,8 +5714,12 @@
       <c r="D242">
         <v>146.30000000000001</v>
       </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K242">
+        <f t="shared" si="3"/>
+        <v>33.616727941176471</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>245</v>
       </c>
@@ -4681,8 +5732,12 @@
       <c r="D243">
         <v>244.2</v>
       </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K243">
+        <f t="shared" si="3"/>
+        <v>56.112132352941174</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>246</v>
       </c>
@@ -4695,8 +5750,12 @@
       <c r="D244">
         <v>244.2</v>
       </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K244">
+        <f t="shared" si="3"/>
+        <v>56.112132352941174</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>247</v>
       </c>
@@ -4709,8 +5768,12 @@
       <c r="D245">
         <v>203.4</v>
       </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K245">
+        <f t="shared" si="3"/>
+        <v>46.737132352941174</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>248</v>
       </c>
@@ -4723,8 +5786,12 @@
       <c r="D246">
         <v>203.4</v>
       </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K246">
+        <f t="shared" si="3"/>
+        <v>46.737132352941174</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>249</v>
       </c>
@@ -4737,8 +5804,12 @@
       <c r="D247">
         <v>169.8</v>
       </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K247">
+        <f t="shared" si="3"/>
+        <v>39.016544117647058</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>250</v>
       </c>
@@ -4751,8 +5822,12 @@
       <c r="D248">
         <v>169.8</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K248">
+        <f t="shared" si="3"/>
+        <v>39.016544117647058</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>251</v>
       </c>
@@ -4765,8 +5840,12 @@
       <c r="D249">
         <v>190.2</v>
       </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K249">
+        <f t="shared" si="3"/>
+        <v>43.704044117647058</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>252</v>
       </c>
@@ -4779,8 +5858,12 @@
       <c r="D250">
         <v>190.2</v>
       </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K250">
+        <f t="shared" si="3"/>
+        <v>43.704044117647058</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>253</v>
       </c>
@@ -4793,8 +5876,12 @@
       <c r="D251">
         <v>202.4</v>
       </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K251">
+        <f t="shared" si="3"/>
+        <v>46.507352941176471</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>254</v>
       </c>
@@ -4807,8 +5894,12 @@
       <c r="D252">
         <v>202.4</v>
       </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K252">
+        <f t="shared" si="3"/>
+        <v>46.507352941176471</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>255</v>
       </c>
@@ -4821,8 +5912,12 @@
       <c r="D253">
         <v>120.7</v>
       </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K253">
+        <f t="shared" si="3"/>
+        <v>27.734375</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>256</v>
       </c>
@@ -4835,8 +5930,12 @@
       <c r="D254">
         <v>120.7</v>
       </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K254">
+        <f t="shared" si="3"/>
+        <v>27.734375</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>257</v>
       </c>
@@ -4849,8 +5948,12 @@
       <c r="D255">
         <v>122.1</v>
       </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K255">
+        <f t="shared" si="3"/>
+        <v>28.056066176470587</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>258</v>
       </c>
@@ -4863,8 +5966,12 @@
       <c r="D256">
         <v>122.1</v>
       </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K256">
+        <f t="shared" si="3"/>
+        <v>28.056066176470587</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>259</v>
       </c>
@@ -4877,8 +5984,12 @@
       <c r="D257">
         <v>144.9</v>
       </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K257">
+        <f t="shared" si="3"/>
+        <v>33.295036764705884</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>260</v>
       </c>
@@ -4891,8 +6002,12 @@
       <c r="D258">
         <v>144.9</v>
       </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K258">
+        <f t="shared" si="3"/>
+        <v>33.295036764705884</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>261</v>
       </c>
@@ -4905,8 +6020,12 @@
       <c r="D259">
         <v>151.9</v>
       </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K259">
+        <f t="shared" ref="K259:K280" si="4">D259*10^6*$H$9/$H$7</f>
+        <v>34.903492647058826</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>262</v>
       </c>
@@ -4919,8 +6038,12 @@
       <c r="D260">
         <v>151.9</v>
       </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K260">
+        <f t="shared" si="4"/>
+        <v>34.903492647058826</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>263</v>
       </c>
@@ -4933,8 +6056,12 @@
       <c r="D261">
         <v>265.2</v>
       </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K261">
+        <f t="shared" si="4"/>
+        <v>60.9375</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>264</v>
       </c>
@@ -4947,8 +6074,12 @@
       <c r="D262">
         <v>265.2</v>
       </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K262">
+        <f t="shared" si="4"/>
+        <v>60.9375</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>265</v>
       </c>
@@ -4961,8 +6092,12 @@
       <c r="D263">
         <v>214.9</v>
       </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K263">
+        <f t="shared" si="4"/>
+        <v>49.379595588235297</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>266</v>
       </c>
@@ -4975,8 +6110,12 @@
       <c r="D264">
         <v>214.9</v>
       </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K264">
+        <f t="shared" si="4"/>
+        <v>49.379595588235297</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>267</v>
       </c>
@@ -4989,8 +6128,12 @@
       <c r="D265">
         <v>163.4</v>
       </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K265">
+        <f t="shared" si="4"/>
+        <v>37.545955882352942</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>268</v>
       </c>
@@ -5003,8 +6146,12 @@
       <c r="D266">
         <v>163.4</v>
       </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K266">
+        <f t="shared" si="4"/>
+        <v>37.545955882352942</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>269</v>
       </c>
@@ -5017,8 +6164,12 @@
       <c r="D267">
         <v>200.9</v>
       </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K267">
+        <f t="shared" si="4"/>
+        <v>46.162683823529413</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>270</v>
       </c>
@@ -5031,8 +6182,12 @@
       <c r="D268">
         <v>200.9</v>
       </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K268">
+        <f t="shared" si="4"/>
+        <v>46.162683823529413</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>271</v>
       </c>
@@ -5045,8 +6200,12 @@
       <c r="D269">
         <v>124.1</v>
       </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K269">
+        <f t="shared" si="4"/>
+        <v>28.515625</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>272</v>
       </c>
@@ -5059,8 +6218,12 @@
       <c r="D270">
         <v>124.1</v>
       </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K270">
+        <f t="shared" si="4"/>
+        <v>28.515625</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>273</v>
       </c>
@@ -5073,8 +6236,12 @@
       <c r="D271">
         <v>228.7</v>
       </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K271">
+        <f t="shared" si="4"/>
+        <v>52.550551470588232</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>274</v>
       </c>
@@ -5087,8 +6254,12 @@
       <c r="D272">
         <v>228.7</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K272">
+        <f t="shared" si="4"/>
+        <v>52.550551470588232</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>275</v>
       </c>
@@ -5101,8 +6272,12 @@
       <c r="D273">
         <v>161.69999999999999</v>
       </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K273">
+        <f t="shared" si="4"/>
+        <v>37.155330882352942</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>276</v>
       </c>
@@ -5115,8 +6290,12 @@
       <c r="D274">
         <v>161.69999999999999</v>
       </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K274">
+        <f t="shared" si="4"/>
+        <v>37.155330882352942</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>277</v>
       </c>
@@ -5129,8 +6308,12 @@
       <c r="D275">
         <v>213.8</v>
       </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K275">
+        <f t="shared" si="4"/>
+        <v>49.126838235294116</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>278</v>
       </c>
@@ -5143,8 +6326,12 @@
       <c r="D276">
         <v>213.8</v>
       </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K276">
+        <f t="shared" si="4"/>
+        <v>49.126838235294116</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>279</v>
       </c>
@@ -5157,8 +6344,12 @@
       <c r="D277">
         <v>162.1</v>
       </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K277">
+        <f t="shared" si="4"/>
+        <v>37.247242647058826</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>280</v>
       </c>
@@ -5171,8 +6362,12 @@
       <c r="D278">
         <v>162.1</v>
       </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K278">
+        <f t="shared" si="4"/>
+        <v>37.247242647058826</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>281</v>
       </c>
@@ -5185,8 +6380,12 @@
       <c r="D279">
         <v>247.2</v>
       </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="K279">
+        <f t="shared" si="4"/>
+        <v>56.801470588235297</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>282</v>
       </c>
@@ -5199,9 +6398,14 @@
       <c r="D280">
         <v>247.2</v>
       </c>
+      <c r="K280">
+        <f t="shared" si="4"/>
+        <v>56.801470588235297</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="H4" formulaRange="1"/>
   </ignoredErrors>
